--- a/data/julio 2026/cartones.xlsx
+++ b/data/julio 2026/cartones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A918EC-6B6A-4470-A39E-E6743C2ACFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D363390E-5954-43CB-B3BB-160E46995F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="2850" windowWidth="15375" windowHeight="7785" xr2:uid="{DF2EE928-F73E-4AAC-BA22-2F9F659AC8B2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF2EE928-F73E-4AAC-BA22-2F9F659AC8B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>codigo</t>
+  </si>
+  <si>
+    <t>cod_cam</t>
+  </si>
+  <si>
+    <t>nombre_cam</t>
+  </si>
+  <si>
+    <t>fecha_liq</t>
+  </si>
+  <si>
+    <t>FechaSalidaCamion</t>
+  </si>
+  <si>
+    <t>chofer</t>
+  </si>
+  <si>
+    <t>cajasret</t>
+  </si>
+  <si>
+    <t>cajasretdev</t>
+  </si>
+  <si>
+    <t>Diferencia</t>
+  </si>
+  <si>
+    <t>Porcentaje retorno</t>
+  </si>
+  <si>
+    <t>cajasbienret</t>
+  </si>
+  <si>
+    <t>cajasbienretdev</t>
+  </si>
+  <si>
+    <t>Diferencia bien</t>
+  </si>
+  <si>
+    <t>Porcentaje retorno bien</t>
+  </si>
+  <si>
+    <t>razon_social</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -385,66 +431,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6234BE-26DB-4DDD-AA4D-FE4023C62BA0}">
-  <dimension ref="D2:E663"/>
+  <dimension ref="A1:O663"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
